--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486458_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486458_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1705</v>
+        <v>4.9809</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4174</v>
+        <v>1.5977</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7531</v>
+        <v>3.3832</v>
       </c>
       <c r="G2" t="n">
         <v>4.3332</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4023</v>
+        <v>0.2127</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5119</v>
+        <v>-0.3317</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9142</v>
+        <v>0.5444</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2315</v>
+        <v>4.0182</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7612</v>
+        <v>1.544</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5297</v>
+        <v>2.4742</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3972</v>
+        <v>0.4252</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7311</v>
+        <v>-0.9637</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3339</v>
+        <v>1.3889</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4889</v>
+        <v>-0.3126</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3359</v>
+        <v>-1.8059</v>
       </c>
       <c r="L3" t="n">
-        <v>0.153</v>
+        <v>1.4933</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0917</v>
+        <v>0.7378</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3951</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4869</v>
+        <v>-0.1044</v>
       </c>
       <c r="P3" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7691</v>
+        <v>0.6153</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8172</v>
+        <v>-0.0336</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0481</v>
+        <v>0.6489</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1952</v>
+        <v>1.8902</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4552</v>
+        <v>1.8902</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5913</v>
+        <v>3.8692</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3637</v>
+        <v>5.0907</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2276</v>
+        <v>-1.2215</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4252</v>
+        <v>2.3972</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9637</v>
+        <v>2.7311</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3889</v>
+        <v>-0.3339</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3126</v>
+        <v>2.4889</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.8059</v>
+        <v>2.3359</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4933</v>
+        <v>0.153</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7378</v>
+        <v>-0.0917</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.3951</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1044</v>
+        <v>-0.4869</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1884</v>
+        <v>0.4068</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2139</v>
+        <v>0.1466</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4023</v>
+        <v>0.2602</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8902</v>
+        <v>0.1952</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8902</v>
+        <v>2.4552</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6684</v>
+        <v>2.757</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3988</v>
+        <v>2.734</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2696</v>
+        <v>0.023</v>
       </c>
       <c r="G5" t="n">
         <v>5.0799</v>
@@ -844,13 +844,13 @@
         <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.019</v>
+        <v>0.0697</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5239</v>
+        <v>-0.1887</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5049</v>
+        <v>0.2584</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2079</v>
+        <v>2.6656</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9535</v>
+        <v>1.1337</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2545</v>
+        <v>1.5319</v>
       </c>
       <c r="G6" t="n">
         <v>0.6787</v>
@@ -922,13 +922,13 @@
         <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.5296</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3509</v>
+        <v>-0.1706</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4229</v>
+        <v>0.7003</v>
       </c>
       <c r="V6" t="n">
         <v>0.3698</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.941</v>
+        <v>2.0403</v>
       </c>
       <c r="E7" t="n">
-        <v>0.075</v>
+        <v>0.1435</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8661</v>
+        <v>1.8969</v>
       </c>
       <c r="G7" t="n">
         <v>1.0233</v>
@@ -1000,13 +1000,13 @@
         <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.06</v>
+        <v>0.0394</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3629</v>
+        <v>-0.2944</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3029</v>
+        <v>0.3338</v>
       </c>
       <c r="V7" t="n">
         <v>0.7602</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3939</v>
+        <v>1.79</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.636</v>
+        <v>-0.4557</v>
       </c>
       <c r="F8" t="n">
-        <v>2.03</v>
+        <v>2.2457</v>
       </c>
       <c r="G8" t="n">
         <v>0.0395</v>
@@ -1078,13 +1078,13 @@
         <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1799</v>
+        <v>0.5759</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0361</v>
+        <v>0.2163</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1438</v>
+        <v>0.3596</v>
       </c>
       <c r="V8" t="n">
         <v>0.7395</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>M. BRAZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1685</v>
+        <v>-0.2335</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3941</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2257</v>
+        <v>-0.2335</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.6133</v>
+        <v>-0.2335</v>
       </c>
       <c r="H9" t="n">
-        <v>0.292</v>
+        <v>0.149</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.9053</v>
+        <v>-0.3825</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6387</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0793</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.718</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9747</v>
+        <v>-0.2335</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2127</v>
+        <v>0.149</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1873</v>
+        <v>-0.3825</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1849</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0721</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1128</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. BRAZ</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2335</v>
+        <v>-0.4228</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-0.6176</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2335</v>
+        <v>0.1949</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2335</v>
+        <v>-2.6133</v>
       </c>
       <c r="H10" t="n">
-        <v>0.149</v>
+        <v>0.292</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3825</v>
+        <v>-2.9053</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-1.6387</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.0793</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.718</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2335</v>
+        <v>-0.9747</v>
       </c>
       <c r="N10" t="n">
-        <v>0.149</v>
+        <v>0.2127</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3825</v>
+        <v>-1.1873</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0.0694</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-0.1514</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1829</v>
+        <v>-2.777</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8792</v>
+        <v>-2.715</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3037</v>
+        <v>-0.062</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3341</v>
+        <v>-4.6772</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2861</v>
+        <v>1.037</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.048</v>
+        <v>-5.7142</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2494</v>
+        <v>-3.7025</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1642</v>
+        <v>0.8244</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4136</v>
+        <v>-4.5269</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0847</v>
+        <v>-0.9747</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4504</v>
+        <v>0.2127</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.6344</v>
+        <v>-1.1873</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6287</v>
+        <v>-0.5125</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3701</v>
+        <v>-0.3377</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2585</v>
+        <v>-0.1749</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5438</v>
+        <v>-2.9304</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0502</v>
+        <v>-1.1027</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4935</v>
+        <v>-1.8277</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.6772</v>
+        <v>-3.3341</v>
       </c>
       <c r="H12" t="n">
-        <v>1.037</v>
+        <v>-0.2861</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.7142</v>
+        <v>-3.048</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.7025</v>
+        <v>-1.2494</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8244</v>
+        <v>0.1642</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.5269</v>
+        <v>-1.4136</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9747</v>
+        <v>-2.0847</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2127</v>
+        <v>-0.4504</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1873</v>
+        <v>-1.6344</v>
       </c>
       <c r="P12" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2793</v>
+        <v>0.8811</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.1466</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6064000000000001</v>
+        <v>0.7345</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3252</v>
+        <v>-1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9879</v>
+        <v>-4.327</v>
       </c>
       <c r="E13" t="n">
         <v>-1.6979</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2901</v>
+        <v>-2.6291</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4887</v>
@@ -1468,13 +1468,13 @@
         <v>0.87</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3904</v>
+        <v>0.0514</v>
       </c>
       <c r="T13" t="n">
         <v>-0.4554</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8459</v>
+        <v>0.5068</v>
       </c>
       <c r="V13" t="n">
         <v>-3.7597</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.0879</v>
+        <v>11.4305</v>
       </c>
       <c r="E14" t="n">
-        <v>5.312199999999998</v>
+        <v>5.654700000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>5.7761</v>
+        <v>5.776000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>1.630200000000001</v>
@@ -1519,19 +1519,19 @@
         <v>-11.0524</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7271</v>
+        <v>4.727099999999998</v>
       </c>
       <c r="K14" t="n">
-        <v>7.408399999999999</v>
+        <v>7.4084</v>
       </c>
       <c r="L14" t="n">
         <v>-2.681299999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.0969</v>
+        <v>-3.096900000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>5.2743</v>
+        <v>5.274299999999999</v>
       </c>
       <c r="O14" t="n">
         <v>-8.3712</v>
@@ -1540,19 +1540,19 @@
         <v>4.3499</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.525099999999999</v>
+        <v>-6.5251</v>
       </c>
       <c r="R14" t="n">
         <v>10.875</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4574</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.7963</v>
+        <v>-1.454</v>
       </c>
       <c r="U14" t="n">
-        <v>4.2537</v>
+        <v>4.254</v>
       </c>
       <c r="V14" t="n">
         <v>2.6503</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4374</v>
+        <v>1.2023</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3824</v>
+        <v>-0.1764</v>
       </c>
       <c r="F15" t="n">
-        <v>1.055</v>
+        <v>1.3787</v>
       </c>
       <c r="G15" t="n">
         <v>1.4086</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5944</v>
+        <v>0.3593</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3942</v>
+        <v>-0.1646</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2002</v>
+        <v>0.5239</v>
       </c>
       <c r="V15" t="n">
         <v>0.7395</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2177</v>
+        <v>0.7559</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.3062</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3119</v>
+        <v>1.0621</v>
       </c>
       <c r="G16" t="n">
         <v>0.481</v>
@@ -1702,13 +1702,13 @@
         <v>0.435</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1338</v>
+        <v>-0.1601</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.5299</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3803</v>
+        <v>0.3698</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3742</v>
+        <v>0.3451</v>
       </c>
       <c r="E17" t="n">
         <v>-0.9500999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5759</v>
+        <v>1.2952</v>
       </c>
       <c r="G17" t="n">
         <v>0.4494</v>
@@ -1780,13 +1780,13 @@
         <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0618</v>
+        <v>-0.3425</v>
       </c>
       <c r="T17" t="n">
         <v>-0.9589</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1029</v>
+        <v>0.6165</v>
       </c>
       <c r="V17" t="n">
         <v>0.0207</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. POLANCO TAVAREZ</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5414</v>
+        <v>0.2297</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6058</v>
+        <v>1.0228</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0645</v>
+        <v>-0.7931</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7565</v>
+        <v>0.5743</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.7614</v>
+        <v>-0.5629</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0048</v>
+        <v>1.1371</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7388</v>
+        <v>2.424</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4655</v>
+        <v>0.949</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7267</v>
+        <v>1.475</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0178</v>
+        <v>-1.8497</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2959</v>
+        <v>-1.5118</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2781</v>
+        <v>-0.3379</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1747</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.822</v>
+        <v>-0.3136</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6472</v>
+        <v>0.4041</v>
       </c>
       <c r="V18" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>E. POLANCO TAVAREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6752</v>
+        <v>-0.2176</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1831</v>
+        <v>-0.1588</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4921</v>
+        <v>-0.0588</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-1.7565</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1766</v>
+        <v>-2.7614</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3259</v>
+        <v>1.0048</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1677</v>
+        <v>-0.7388</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0912</v>
+        <v>-1.4655</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0765</v>
+        <v>0.7267</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6703</v>
+        <v>-1.0178</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2679</v>
+        <v>-1.2959</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4024</v>
+        <v>0.2781</v>
       </c>
       <c r="P19" t="n">
-        <v>0.435</v>
+        <v>-0.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R19" t="n">
         <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7175</v>
+        <v>0.149</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3509</v>
+        <v>-0.3749</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0684</v>
+        <v>0.5239</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3252</v>
+        <v>2.2599</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7501</v>
+        <v>-0.235</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.09</v>
+        <v>-0.2018</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6601</v>
+        <v>-0.0333</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8632</v>
@@ -2014,13 +2014,13 @@
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3306</v>
+        <v>0.8457</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2572</v>
+        <v>0.1454</v>
       </c>
       <c r="U20" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.7003</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>M. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0664</v>
+        <v>-0.8587</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2405</v>
+        <v>0.3363</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3069</v>
+        <v>-1.195</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5743</v>
+        <v>-2.0334</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5629</v>
+        <v>-2.6733</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1371</v>
+        <v>0.6399</v>
       </c>
       <c r="J21" t="n">
-        <v>2.424</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.949</v>
+        <v>-1.7575</v>
       </c>
       <c r="L21" t="n">
-        <v>1.475</v>
+        <v>0.9778</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8497</v>
+        <v>-1.2537</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5118</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="O21" t="n">
         <v>-0.3379</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2057</v>
+        <v>0.4792</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0959</v>
+        <v>-0.3821</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1097</v>
+        <v>0.8613</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.1745</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.7156</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MWEMA</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.957</v>
+        <v>-1.1491</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2868</v>
+        <v>-0.5184</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3298</v>
+        <v>-0.6307</v>
       </c>
       <c r="G22" t="n">
-        <v>1.557</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9794</v>
+        <v>-0.1766</v>
       </c>
       <c r="I22" t="n">
-        <v>2.5364</v>
+        <v>-0.3259</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3881</v>
+        <v>0.1677</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1251</v>
+        <v>0.0912</v>
       </c>
       <c r="L22" t="n">
-        <v>1.5133</v>
+        <v>0.0765</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1688</v>
+        <v>-0.6703</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1457</v>
+        <v>-0.2679</v>
       </c>
       <c r="O22" t="n">
-        <v>1.0231</v>
+        <v>-0.4024</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4487</v>
+        <v>0.2436</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2824</v>
+        <v>-0.6862</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1663</v>
+        <v>0.9298</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3252</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. GEU</t>
+          <t>J. MWEMA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1374</v>
+        <v>-1.3623</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.306</v>
+        <v>-2.6221</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8314</v>
+        <v>1.2598</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1824</v>
+        <v>1.557</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2987</v>
+        <v>-0.9794</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8837</v>
+        <v>2.5364</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7000999999999999</v>
+        <v>0.3881</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0698</v>
+        <v>-1.1251</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6303</v>
+        <v>1.5133</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4823</v>
+        <v>1.1688</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2289</v>
+        <v>0.1457</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2534</v>
+        <v>1.0231</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6525</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R23" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>1.8275</v>
+        <v>0.146</v>
       </c>
       <c r="T23" t="n">
-        <v>1.4817</v>
+        <v>-0.6177</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3458</v>
+        <v>0.7637</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. TORRES CUEVAS</t>
+          <t>Y. JOSEPH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3398</v>
+        <v>-2.0115</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.446</v>
+        <v>-0.7778</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8937</v>
+        <v>-1.2336</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.0334</v>
+        <v>1.2379</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.6733</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6399</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7796999999999999</v>
+        <v>1.0451</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.7575</v>
+        <v>1.0069</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9778</v>
+        <v>0.0382</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2537</v>
+        <v>0.1927</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.3834</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3379</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>0.87</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R24" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0019</v>
+        <v>-0.4461</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1644</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1626</v>
+        <v>0.2893</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1745</v>
+        <v>-1.7156</v>
       </c>
       <c r="W24" t="n">
-        <v>1.7156</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.8902</v>
+        <v>-1.7156</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Y. JOSEPH</t>
+          <t>D. GEU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.4662</v>
+        <v>-3.3166</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.0014</v>
+        <v>-1.4235</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4649</v>
+        <v>-1.8931</v>
       </c>
       <c r="G25" t="n">
-        <v>1.2379</v>
+        <v>-2.1824</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6235000000000001</v>
+        <v>-1.2987</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6143999999999999</v>
+        <v>-0.8837</v>
       </c>
       <c r="J25" t="n">
-        <v>1.0451</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>1.0069</v>
+        <v>-0.0698</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0382</v>
+        <v>-0.6303</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1927</v>
+        <v>-1.4823</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.3834</v>
+        <v>-1.2289</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5760999999999999</v>
+        <v>-0.2534</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.0875</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q25" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9009</v>
+        <v>0.6483</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9589</v>
+        <v>0.3641</v>
       </c>
       <c r="U25" t="n">
-        <v>0.058</v>
+        <v>0.2842</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.7156</v>
+        <v>-1.13</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.7156</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.088</v>
+        <v>-6.6178</v>
       </c>
       <c r="E26" t="n">
         <v>-5.776</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.312</v>
+        <v>-0.8417999999999997</v>
       </c>
       <c r="G26" t="n">
         <v>-1.629799999999999</v>
@@ -2464,16 +2464,16 @@
         <v>8.371</v>
       </c>
       <c r="M26" t="n">
-        <v>-4.7273</v>
+        <v>-4.727300000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>-7.4084</v>
+        <v>-7.408400000000001</v>
       </c>
       <c r="O26" t="n">
         <v>2.6812</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.350099999999999</v>
+        <v>-4.3501</v>
       </c>
       <c r="Q26" t="n">
         <v>-10.8752</v>
@@ -2482,13 +2482,13 @@
         <v>6.524999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.4575</v>
+        <v>2.0128</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.2538</v>
+        <v>-4.253800000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>1.7964</v>
+        <v>6.2668</v>
       </c>
       <c r="V26" t="n">
         <v>-2.650399999999999</v>
